--- a/sharedata/excel/D-单位等级表(UnitLevelData).xlsx
+++ b/sharedata/excel/D-单位等级表(UnitLevelData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -535,6 +535,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -660,13 +667,6 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="34">
@@ -995,148 +995,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1166,13 +1166,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1677,7 +1677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2135,7 +2135,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="2:10" ht="33.0" customHeight="1">
+    <row r="21" spans="2:10">
       <c r="B21" s="7">
         <v>20005</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="33.0" customHeight="1">
+    <row r="26" spans="2:10">
       <c r="B26" s="7">
         <v>20010</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="2:10" ht="33.0" customHeight="1">
+    <row r="31" spans="2:10">
       <c r="B31" s="7">
         <v>20015</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="2:10" ht="33.0" customHeight="1">
+    <row r="36" spans="2:10">
       <c r="B36" s="7">
         <v>20020</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="2:10" ht="33.0" customHeight="1">
+    <row r="41" spans="2:10">
       <c r="B41" s="7">
         <v>20025</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="2:10" ht="33.0" customHeight="1">
+    <row r="46" spans="2:10">
       <c r="B46" s="7">
         <v>20030</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="2:10" ht="33.0" customHeight="1">
+    <row r="51" spans="2:10">
       <c r="B51" s="7">
         <v>20035</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="2:10" ht="33.0" customHeight="1">
+    <row r="56" spans="2:10">
       <c r="B56" s="7">
         <v>20040</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="61" spans="2:10" ht="33.0" customHeight="1">
+    <row r="61" spans="2:10">
       <c r="B61" s="7">
         <v>20045</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="66" spans="2:10" ht="33.0" customHeight="1">
+    <row r="66" spans="2:10">
       <c r="B66" s="7">
         <v>20050</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="71" spans="2:10" ht="33.0" customHeight="1">
+    <row r="71" spans="2:10">
       <c r="B71" s="7">
         <v>20055</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="76" spans="2:10" ht="33.0" customHeight="1">
+    <row r="76" spans="2:10">
       <c r="B76" s="7">
         <v>20060</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="81" spans="2:10" ht="33.0" customHeight="1">
+    <row r="81" spans="2:10">
       <c r="B81" s="7">
         <v>20065</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="86" spans="2:10" ht="33.0" customHeight="1">
+    <row r="86" spans="2:10">
       <c r="B86" s="7">
         <v>20070</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="91" spans="2:10" ht="33.0" customHeight="1">
+    <row r="91" spans="2:10">
       <c r="B91" s="7">
         <v>20075</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="96" spans="2:10" ht="33.0" customHeight="1">
+    <row r="96" spans="2:10">
       <c r="B96" s="7">
         <v>20080</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="101" spans="2:10" ht="33.0" customHeight="1">
+    <row r="101" spans="2:10">
       <c r="B101" s="7">
         <v>20085</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="106" spans="2:10" ht="33.0" customHeight="1">
+    <row r="106" spans="2:10">
       <c r="B106" s="7">
         <v>20090</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="111" spans="2:10" ht="33.0" customHeight="1">
+    <row r="111" spans="2:10">
       <c r="B111" s="7">
         <v>20095</v>
       </c>
